--- a/artfynd/A 49328-2023 artfynd.xlsx
+++ b/artfynd/A 49328-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119625421</v>
+        <v>119625422</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543603</v>
+        <v>543590</v>
       </c>
       <c r="R2" t="n">
-        <v>6966927</v>
+        <v>6966932</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119625422</v>
+        <v>119625421</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543590</v>
+        <v>543603</v>
       </c>
       <c r="R3" t="n">
-        <v>6966932</v>
+        <v>6966927</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 49328-2023 artfynd.xlsx
+++ b/artfynd/A 49328-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119625422</v>
+        <v>119625421</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
+        <v>90562</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543590</v>
+        <v>543603</v>
       </c>
       <c r="R2" t="n">
-        <v>6966932</v>
+        <v>6966927</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119625421</v>
+        <v>119625422</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543603</v>
+        <v>543590</v>
       </c>
       <c r="R3" t="n">
-        <v>6966927</v>
+        <v>6966932</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 49328-2023 artfynd.xlsx
+++ b/artfynd/A 49328-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119625421</v>
+        <v>119625422</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543603</v>
+        <v>543590</v>
       </c>
       <c r="R2" t="n">
-        <v>6966927</v>
+        <v>6966932</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119625422</v>
+        <v>119625421</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543590</v>
+        <v>543603</v>
       </c>
       <c r="R3" t="n">
-        <v>6966932</v>
+        <v>6966927</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 49328-2023 artfynd.xlsx
+++ b/artfynd/A 49328-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625422</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,8 +876,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119625421</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>